--- a/data/archive/2026-09-27.xlsx
+++ b/data/archive/2026-09-27.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,8 +31,19 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <color rgb="000563C1"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +53,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F6F8FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -68,17 +84,28 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -441,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -550,8 +577,1471 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Business Systems Engineer, Tech Foundations</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>8214444</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com/positions/8214444?gh_jid=8214444</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27 23:25 UTC</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Figma</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern (Summer 2027)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>San Francisco, CA • New York, NY</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>6143238004</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/figma/jobs/6143238004?gh_jid=6143238004</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27 23:25 UTC</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Lyft</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Backend Software Engineer, Airports</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8806570002</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8806570002?gh_jid=8806570002</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27 23:25 UTC</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Scale AI</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer, Public Sector - New Grad</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>4736426005</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/scaleai/jobs/4736426005</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27 23:25 UTC</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer, Intern</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>New York, NY; Pittsburgh, PA; Seattle, WA</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>8805925002</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>https://careers.duolingo.com/jobs/8805925002?gh_jid=8805925002</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27 23:25 UTC</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer, Thrive Intern</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>8806114002</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>https://careers.duolingo.com/jobs/8806114002?gh_jid=8806114002</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27 23:25 UTC</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Asana</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Senior Staff Software Engineer, Developer Productivity</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>8212172</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.asana.com/jobs/apply/8212172?gh_jid=8212172</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27 23:25 UTC</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Nuro</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Embedded Software Engineer</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Mountain View, California (HQ)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>8180955</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>https://nuro.ai/careersitem?gh_jid=8180955</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27 23:25 UTC</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Mercury</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern - Spring 2027</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, New York, NY, Portland, OR, or Remote within Canada or United States</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6199367004</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/mercury/jobs/6199367004</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27 23:25 UTC</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Robinhood</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern, Android (Summer 2027)</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Menlo Park, CA; New York, NY</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>8142961</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood/jobs/8142961?gh_jid=8142961&amp;t=gh_src%3D</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27 23:25 UTC</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Robinhood</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern, Backend (Summer 2027)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Bellevue, WA; Menlo Park, CA; New York, NY</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>8123225</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood/jobs/8123225?gh_jid=8123225&amp;t=gh_src%3D</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27 23:25 UTC</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Robinhood</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern, iOS (Summer 2027)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Menlo Park, CA; New York, NY</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>8142959</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood/jobs/8142959?gh_jid=8142959&amp;t=gh_src%3D</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27 23:25 UTC</t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P13" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Robinhood</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern, Web (Summer 2027)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Menlo Park, CA; New York, NY</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>8142963</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood/jobs/8142963?gh_jid=8142963&amp;t=gh_src%3D</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27 23:25 UTC</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Notion</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern, Mobile (Winter 2027)</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>San Francisco, California; New York, New York; New York, New York, United States; San Francisco, California, United States</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>2b587e66-deac-421a-a824-9415ba78b5a7</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>ashby</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/notion/2b587e66-deac-421a-a824-9415ba78b5a7</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27 23:25 UTC</t>
+        </is>
+      </c>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P15" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q15" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Cybersecurity Engineer, Junior</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Security Engineer</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>El Segundo, CA</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>R0250290</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/job/El-Segundo-CA/Cybersecurity-Engineer--Junior_R0250290</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27 23:28 UTC</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>University - 2027 Summer Games Systems Engineer Intern - Rome, NY</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Rome, NY</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>R0248386</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/job/Rome-NY/University---2027-Summer-Games-Systems-Engineer-Intern---Rome--NY_R0248386</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27 23:28 UTC</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P17" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q17" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>University, 2027 Summer Games Software Developer Intern - McLean, VA</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>McLean, VA</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>R0248029</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/job/McLean-VA/University--2027-Summer-Games-Software-Developer-Intern_R0248029</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27 23:28 UTC</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q2"/>
+  <autoFilter ref="A1:Q18"/>
   <dataValidations count="2">
     <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Applied" error="Select a value from the list" type="list">
       <formula1>"☐ Not Applied,☑ Applied"</formula1>
@@ -560,6 +2050,25 @@
       <formula1>"Not Started,Applied,OA,Recruiter Screen,Interview,Rejected,Offer,Withdrawn"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>